--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.139.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.139.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0139.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0139.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œmore deta</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+8C61 CJK UNIFIED IDEOGRAPH-8C61 | isolated marker/symbol line :: 象</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: agreement,â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]132</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]132</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L27: isolated marker/symbol line :: 1</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 7.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]132</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -657,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: è±¡</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: 一, the</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sum of Â£â€”</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: agreement,€</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -683,7 +687,11 @@
           <t>L36: isolated marker/symbol line :: 132</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: 7.</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
@@ -691,7 +699,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The character of the plaintiff must be described, without detail-</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -721,28 +733,24 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: ä¸€, the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------term, in the year ----------(or G. H. late of</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The character of the plaintiff must be described, without detail-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: è±¡</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+8C61 CJK UNIFIED IDEOGRAPH-8C61 | isolated marker/symbol line :: 象</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------term, in the year ----------(or G. H. late of</t>
+          <t>L97: punctuation artifact: double/multiple hyphen :: — --------term, in the year ----------(or G. H. late of</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -762,7 +770,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -777,11 +785,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ The character of the plaintiff must be described, without detail-</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -887,7 +891,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L106: punctuation artifact: double/multiple hyphen :: defendant hereinafter named, for the sum of Â£----, in an</t>
+          <t>L106: punctuation artifact: double/multiple hyphen :: defendant hereinafter named, for the sum of £----, in an</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -993,12 +997,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1037,7 +1041,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1076,7 +1080,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1154,7 +1158,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
